--- a/data/trans_camb/P13_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P13_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 5,41</t>
+          <t>-1,12; 4,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 6,03</t>
+          <t>-0,79; 5,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,12</t>
+          <t>-4,09; 0,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,98; 20,84</t>
+          <t>9,7; 20,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 11,12</t>
+          <t>2,18; 11,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,09; -0,02</t>
+          <t>-5,3; -0,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,67; 11,7</t>
+          <t>5,47; 11,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,84</t>
+          <t>2,03; 7,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; -0,13</t>
+          <t>-3,68; -0,3</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 331,09</t>
+          <t>-34,61; 293,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 381,47</t>
+          <t>-24,21; 431,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-86,16; 94,79</t>
+          <t>-86,79; 111,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>180,47; 1125,75</t>
+          <t>161,31; 1128,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,74; 682,09</t>
+          <t>28,64; 611,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-90,45; 47,24</t>
+          <t>-93,69; 2,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>125,64; 546,89</t>
+          <t>126,74; 601,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,06; 358,24</t>
+          <t>43,28; 382,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-81,22; 5,22</t>
+          <t>-83,43; -3,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,75</t>
+          <t>-2,68; 2,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; -0,03</t>
+          <t>-4,97; -0,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 2,27</t>
+          <t>-3,45; 2,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 7,74</t>
+          <t>1,02; 8,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,83; -0,21</t>
+          <t>-5,9; -0,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 3,94</t>
+          <t>-2,05; 4,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 4,48</t>
+          <t>0,08; 4,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; -0,75</t>
+          <t>-4,5; -0,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 2,27</t>
+          <t>-1,69; 2,21</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,76; 87,75</t>
+          <t>-45,29; 92,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-76,81; 5,61</t>
+          <t>-77,34; 1,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,54; 70,91</t>
+          <t>-55,45; 77,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 149,4</t>
+          <t>10,58; 166,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-71,59; -0,11</t>
+          <t>-69,51; -2,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,09; 80,26</t>
+          <t>-25,75; 80,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 98,1</t>
+          <t>0,32; 101,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,02; -15,51</t>
+          <t>-66,6; -16,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,62; 50,12</t>
+          <t>-25,62; 51,51</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 4,55</t>
+          <t>-0,6; 4,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,01</t>
+          <t>-1,75; 2,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 9,82</t>
+          <t>3,41; 9,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 7,5</t>
+          <t>1,37; 7,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,03</t>
+          <t>-3,46; 0,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,67; 11,69</t>
+          <t>5,51; 11,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,21</t>
+          <t>1,03; 5,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,57</t>
+          <t>-2,17; 0,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,34; 9,59</t>
+          <t>5,34; 9,8</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-60,57; 1074,3</t>
+          <t>-53,37; 1162,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-91,7; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>110,44; 2833,47</t>
+          <t>95,51; 2617,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,49; 669,16</t>
+          <t>25,66; 758,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 70,43</t>
+          <t>-100,0; 115,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>142,82; 1230,49</t>
+          <t>121,68; 1043,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,09; 507,31</t>
+          <t>23,57; 521,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,95; 77,41</t>
+          <t>-81,11; 80,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>198,88; 1002,09</t>
+          <t>169,11; 978,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,41</t>
+          <t>-0,76; 3,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,9</t>
+          <t>0,87; 5,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,02; 8,35</t>
+          <t>2,2; 8,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 9,82</t>
+          <t>3,57; 9,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 7,95</t>
+          <t>1,51; 7,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 5,49</t>
+          <t>-0,17; 5,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,08</t>
+          <t>2,2; 6,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,16</t>
+          <t>2,06; 6,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,0</t>
+          <t>2,0; 6,15</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-51,43; 633,71</t>
+          <t>-50,36; 724,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 1241,45</t>
+          <t>-7,13; 1142,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39,03; 1775,36</t>
+          <t>53,63; 1851,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81,36; 674,24</t>
+          <t>80,35; 707,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>41,24; 583,06</t>
+          <t>31,29; 555,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 401,01</t>
+          <t>-5,05; 394,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>79,5; 559,62</t>
+          <t>68,73; 524,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>71,8; 524,29</t>
+          <t>68,28; 522,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>61,41; 477,77</t>
+          <t>76,1; 572,08</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,35</t>
+          <t>-2,62; 3,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,52</t>
+          <t>-1,87; 4,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,73</t>
+          <t>-1,24; 4,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 10,65</t>
+          <t>-0,37; 10,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 5,35</t>
+          <t>-4,18; 5,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 1,84</t>
+          <t>-6,19; 1,79</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 6,17</t>
+          <t>-0,63; 5,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 3,68</t>
+          <t>-2,18; 3,54</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 2,25</t>
+          <t>-2,59; 2,38</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-74,26; 277,63</t>
+          <t>-71,07; 312,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-57,01; 342,9</t>
+          <t>-52,5; 356,46</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 405,43</t>
+          <t>-35,46; 411,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 238,48</t>
+          <t>-7,85; 254,88</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-48,3; 125,22</t>
+          <t>-47,27; 152,66</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-64,71; 49,52</t>
+          <t>-60,71; 53,98</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 204,53</t>
+          <t>-14,2; 180,53</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-39,3; 118,89</t>
+          <t>-38,36; 109,11</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-40,95; 70,97</t>
+          <t>-40,6; 80,82</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,45</t>
+          <t>2,3; 7,65</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,76</t>
+          <t>2,04; 6,77</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,98</t>
+          <t>3,48; 7,59</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,03</t>
+          <t>1,36; 7,96</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,45; 10,61</t>
+          <t>2,38; 10,09</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,88; 9,7</t>
+          <t>4,12; 10,05</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,78</t>
+          <t>2,49; 6,46</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,64</t>
+          <t>3,01; 7,88</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,83</t>
+          <t>4,44; 7,91</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 887,54</t>
+          <t>-0,98; 853,56</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>38,15; 1050,76</t>
+          <t>36,25; 1108,0</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>70,66; 1154,1</t>
+          <t>89,55; 1266,87</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>102,23; 1442,87</t>
+          <t>113,12; 1641,47</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>161,87; 1680,92</t>
+          <t>170,43; 1976,91</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>216,65; 1938,05</t>
+          <t>189,58; 1979,82</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,5; -0,26</t>
+          <t>-4,25; -0,17</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,95</t>
+          <t>-2,68; 1,97</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,74</t>
+          <t>-0,35; 4,81</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 1,53</t>
+          <t>-3,73; 1,56</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 3,66</t>
+          <t>-2,02; 3,53</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 3,64</t>
+          <t>-4,26; 3,52</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,05</t>
+          <t>-3,42; 0,03</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,17</t>
+          <t>-1,45; 2,29</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,4</t>
+          <t>-1,85; 3,28</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-75,47; 3,97</t>
+          <t>-73,49; 5,64</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-50,36; 60,97</t>
+          <t>-48,98; 61,67</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 139,69</t>
+          <t>-7,76; 141,32</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-49,76; 30,87</t>
+          <t>-48,51; 30,59</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-28,96; 69,78</t>
+          <t>-25,14; 67,95</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-49,84; 61,72</t>
+          <t>-53,19; 58,46</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-53,04; 1,33</t>
+          <t>-53,42; 0,8</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-24,68; 47,14</t>
+          <t>-22,59; 51,18</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-25,91; 70,61</t>
+          <t>-25,48; 68,54</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,15</t>
+          <t>1,94; 7,2</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,28</t>
+          <t>-3,63; 0,48</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 1,81</t>
+          <t>-3,54; 1,67</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,54</t>
+          <t>1,33; 7,12</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 0,34</t>
+          <t>-4,69; -0,08</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 3,76</t>
+          <t>-1,08; 3,68</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,52</t>
+          <t>2,52; 6,28</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,57; -0,5</t>
+          <t>-3,42; -0,4</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,85</t>
+          <t>-2,3; 1,83</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>36,08; 202,7</t>
+          <t>35,07; 212,96</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-62,59; 10,13</t>
+          <t>-64,2; 17,26</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-66,01; 44,38</t>
+          <t>-64,13; 45,61</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>24,44; 174,2</t>
+          <t>17,56; 152,89</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-62,91; 8,37</t>
+          <t>-63,62; -0,22</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 83,5</t>
+          <t>-16,49; 78,1</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,13; 147,16</t>
+          <t>42,23; 142,79</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-58,16; -8,96</t>
+          <t>-57,09; -8,78</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-39,1; 40,21</t>
+          <t>-37,52; 38,55</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,49</t>
+          <t>0,36; 2,5</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,08</t>
+          <t>-0,66; 1,21</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,75</t>
+          <t>0,48; 2,69</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3,2; 5,74</t>
+          <t>3,3; 5,8</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,79</t>
+          <t>-0,33; 1,81</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,05</t>
+          <t>0,52; 3,21</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,72</t>
+          <t>2,28; 3,8</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,19</t>
+          <t>-0,23; 1,27</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,58</t>
+          <t>0,89; 2,6</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>12,65; 87,05</t>
+          <t>9,0; 89,38</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 37,89</t>
+          <t>-18,14; 44,29</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>12,19; 101,55</t>
+          <t>13,83; 94,27</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>59,61; 133,82</t>
+          <t>60,4; 133,07</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 41,35</t>
+          <t>-5,9; 42,1</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>7,59; 70,61</t>
+          <t>9,97; 74,16</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>47,49; 99,88</t>
+          <t>51,46; 102,31</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 31,99</t>
+          <t>-5,34; 34,72</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>21,51; 71,03</t>
+          <t>21,36; 70,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P13_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P13_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,33</t>
+          <t>-1,56</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,22</t>
+          <t>-2,33</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,76</t>
+          <t>-1,94</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,91</t>
+          <t>-0,75; 5,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 5,94</t>
+          <t>-0,57; 5,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 0,99</t>
+          <t>-4,5; 0,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,7; 20,77</t>
+          <t>9,36; 20,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 11,04</t>
+          <t>2,2; 11,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,3; -0,37</t>
+          <t>-5,55; -0,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 11,92</t>
+          <t>5,54; 11,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,47</t>
+          <t>2,12; 7,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,3</t>
+          <t>-3,94; -0,53</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-46,57%</t>
+          <t>-54,78%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-66,62%</t>
+          <t>-69,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-57,05%</t>
+          <t>-62,85%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,61; 293,69</t>
+          <t>-23,57; 335,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 431,9</t>
+          <t>-23,34; 337,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-86,79; 111,9</t>
+          <t>-92,09; 44,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161,31; 1128,39</t>
+          <t>162,28; 1123,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,64; 611,0</t>
+          <t>33,07; 584,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-93,69; 2,27</t>
+          <t>-90,95; 0,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>126,74; 601,42</t>
+          <t>115,5; 542,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>43,28; 382,0</t>
+          <t>42,01; 335,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-83,43; -3,89</t>
+          <t>-84,77; -17,98</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>-0,42</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 2,93</t>
+          <t>-2,8; 2,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,97; -0,08</t>
+          <t>-4,8; 0,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 2,34</t>
+          <t>-3,27; 2,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 8,16</t>
+          <t>0,53; 8,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -0,32</t>
+          <t>-6,05; -0,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 4,16</t>
+          <t>-2,13; 3,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,53</t>
+          <t>0,01; 4,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,5; -0,85</t>
+          <t>-4,62; -0,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,21</t>
+          <t>-1,81; 2,19</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-9,32%</t>
+          <t>-9,12%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,29; 92,07</t>
+          <t>-48,97; 96,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-77,34; 1,73</t>
+          <t>-76,72; 9,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-55,45; 77,29</t>
+          <t>-55,0; 75,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,58; 166,37</t>
+          <t>5,02; 157,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,51; -2,93</t>
+          <t>-70,85; -1,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,75; 80,43</t>
+          <t>-28,15; 74,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 101,25</t>
+          <t>-2,08; 96,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,6; -16,51</t>
+          <t>-66,73; -14,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 51,51</t>
+          <t>-28,99; 49,14</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,34</t>
+          <t>6,19</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,58</t>
+          <t>8,68</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,35</t>
+          <t>-0,57; 4,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,02</t>
+          <t>-1,68; 1,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 9,6</t>
+          <t>3,61; 9,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 7,59</t>
+          <t>1,33; 7,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,16</t>
+          <t>-3,58; 0,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 11,62</t>
+          <t>5,67; 11,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,15</t>
+          <t>1,14; 4,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,53</t>
+          <t>-2,08; 0,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,34; 9,8</t>
+          <t>5,57; 9,65</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>546,93%</t>
+          <t>533,92%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>395,77%</t>
+          <t>400,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>449,22%</t>
+          <t>449,11%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-53,37; 1162,02</t>
+          <t>-65,03; 1117,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-91,7; —</t>
+          <t>-100,0; 794,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95,51; 2617,7</t>
+          <t>79,96; 2451,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,66; 758,57</t>
+          <t>24,1; 675,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 115,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>121,68; 1043,75</t>
+          <t>121,22; 1116,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,57; 521,42</t>
+          <t>37,78; 486,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,11; 80,89</t>
+          <t>-81,02; 63,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>169,11; 978,49</t>
+          <t>184,66; 998,61</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>4,32</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>4,34</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,94</t>
+          <t>4,35</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,38</t>
+          <t>-0,9; 3,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,8</t>
+          <t>0,84; 5,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 8,54</t>
+          <t>1,7; 7,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,57; 9,95</t>
+          <t>3,61; 10,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 7,78</t>
+          <t>1,97; 8,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 5,71</t>
+          <t>1,75; 6,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,09</t>
+          <t>2,1; 6,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 6,02</t>
+          <t>2,09; 6,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,15</t>
+          <t>2,6; 6,39</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>392,64%</t>
+          <t>338,51%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>123,45%</t>
+          <t>176,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>209,34%</t>
+          <t>231,59%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,36; 724,61</t>
+          <t>-56,17; 727,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 1142,37</t>
+          <t>0,09; 1115,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53,63; 1851,37</t>
+          <t>44,34; 1908,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80,35; 707,84</t>
+          <t>83,52; 720,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,29; 555,35</t>
+          <t>43,7; 598,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 394,0</t>
+          <t>38,33; 466,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,73; 524,43</t>
+          <t>69,99; 509,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>68,28; 522,95</t>
+          <t>71,4; 526,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>76,1; 572,08</t>
+          <t>86,6; 536,37</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>-1,83</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>-0,28</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 3,65</t>
+          <t>-3,39; 3,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 4,49</t>
+          <t>-2,24; 4,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,78</t>
+          <t>-1,72; 3,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 10,67</t>
+          <t>-0,91; 10,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 5,93</t>
+          <t>-4,02; 5,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 1,79</t>
+          <t>-6,08; 1,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 5,83</t>
+          <t>-0,76; 5,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 3,54</t>
+          <t>-2,03; 3,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 2,38</t>
+          <t>-2,68; 1,98</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-25,21%</t>
+          <t>-27,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>-6,02%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-71,07; 312,63</t>
+          <t>-77,9; 269,28</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-52,5; 356,46</t>
+          <t>-66,29; 346,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-35,46; 411,91</t>
+          <t>-47,01; 332,89</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 254,88</t>
+          <t>-11,45; 242,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-47,27; 152,66</t>
+          <t>-45,04; 150,06</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-60,71; 53,98</t>
+          <t>-62,11; 50,06</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 180,53</t>
+          <t>-13,2; 178,18</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-38,36; 109,11</t>
+          <t>-34,32; 118,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-40,6; 80,82</t>
+          <t>-42,9; 63,63</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>6,85</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6,12</t>
+          <t>6,04</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,65</t>
+          <t>2,31; 7,43</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,77</t>
+          <t>1,98; 7,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,59</t>
+          <t>3,72; 7,78</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,96</t>
+          <t>1,28; 7,6</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,38; 10,09</t>
+          <t>2,53; 10,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,12; 10,05</t>
+          <t>4,01; 9,58</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,46</t>
+          <t>2,5; 6,64</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,88</t>
+          <t>2,97; 7,45</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,91</t>
+          <t>4,34; 7,84</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>365,56%</t>
+          <t>357,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>631,68%</t>
+          <t>623,36%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 853,56</t>
+          <t>9,31; 1037,9</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>36,25; 1108,0</t>
+          <t>57,24; 1768,41</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>89,55; 1266,87</t>
+          <t>101,22; 1518,59</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>113,12; 1641,47</t>
+          <t>116,45; 1548,06</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>170,43; 1976,91</t>
+          <t>143,03; 1895,82</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>189,58; 1979,82</t>
+          <t>214,4; 1981,4</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,15</t>
+          <t>2,71</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>2,83</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,25; -0,17</t>
+          <t>-4,59; -0,07</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 1,97</t>
+          <t>-2,64; 2,18</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 4,81</t>
+          <t>-0,14; 5,61</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 1,56</t>
+          <t>-3,85; 1,33</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 3,53</t>
+          <t>-1,93; 3,76</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 3,52</t>
+          <t>0,26; 5,49</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 0,03</t>
+          <t>-3,45; -0,01</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,29</t>
+          <t>-1,53; 2,3</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,28</t>
+          <t>0,95; 4,92</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-73,49; 5,64</t>
+          <t>-76,2; 3,86</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-48,98; 61,67</t>
+          <t>-45,06; 70,08</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 141,32</t>
+          <t>-6,91; 174,05</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-48,51; 30,59</t>
+          <t>-49,21; 25,76</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-25,14; 67,95</t>
+          <t>-26,15; 73,21</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-53,19; 58,46</t>
+          <t>3,81; 109,56</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-53,42; 0,8</t>
+          <t>-55,51; -1,24</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-22,59; 51,18</t>
+          <t>-24,47; 51,75</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-25,48; 68,54</t>
+          <t>13,52; 109,65</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>1,51</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>1,07</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,94; 7,2</t>
+          <t>1,92; 7,08</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 0,48</t>
+          <t>-3,57; 0,34</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,67</t>
+          <t>-1,33; 2,74</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,12</t>
+          <t>1,64; 7,17</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,69; -0,08</t>
+          <t>-4,54; -0,33</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,68</t>
+          <t>-0,83; 3,63</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,28</t>
+          <t>2,43; 6,41</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,42; -0,4</t>
+          <t>-3,4; -0,39</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,83</t>
+          <t>-0,82; 2,5</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-14,55%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>35,07; 212,96</t>
+          <t>36,98; 215,2</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-64,2; 17,26</t>
+          <t>-64,19; 11,01</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-64,13; 45,61</t>
+          <t>-26,04; 83,01</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17,56; 152,89</t>
+          <t>20,37; 154,43</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-63,62; -0,22</t>
+          <t>-64,16; -6,67</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 78,1</t>
+          <t>-11,86; 81,35</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>42,23; 142,79</t>
+          <t>38,66; 150,47</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-57,09; -8,78</t>
+          <t>-56,02; -6,91</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-37,52; 38,55</t>
+          <t>-12,69; 59,51</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>2,61</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1,85</t>
+          <t>2,34</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,5</t>
+          <t>0,6; 2,63</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,21</t>
+          <t>-0,61; 1,14</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,69</t>
+          <t>1,09; 3,07</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,8</t>
+          <t>3,3; 5,74</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,81</t>
+          <t>-0,52; 1,72</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,21</t>
+          <t>1,58; 3,66</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,8</t>
+          <t>2,16; 3,81</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,27</t>
+          <t>-0,18; 1,25</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,6</t>
+          <t>1,66; 3,02</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>58,08%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>9,0; 89,38</t>
+          <t>15,65; 97,16</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 44,29</t>
+          <t>-17,34; 40,33</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>13,83; 94,27</t>
+          <t>29,4; 112,43</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>60,4; 133,07</t>
+          <t>60,87; 133,53</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 42,1</t>
+          <t>-9,66; 39,7</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>9,97; 74,16</t>
+          <t>28,17; 87,91</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>51,46; 102,31</t>
+          <t>50,02; 104,39</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 34,72</t>
+          <t>-4,3; 33,43</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>21,36; 70,38</t>
+          <t>38,17; 83,38</t>
         </is>
       </c>
     </row>
